--- a/api/templates/devices_and_sites_overview/en.xlsx
+++ b/api/templates/devices_and_sites_overview/en.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\devices_and_sites_overview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBA5657-AA82-43CA-BE21-7D01413481C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71711033-3729-4CB7-A5A6-C469B5B85F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>&lt;Table&gt;</t>
   </si>
@@ -99,6 +99,12 @@
   </si>
   <si>
     <t>Notes: this report only includes the consumables that were sometime tracked on the sites</t>
+  </si>
+  <si>
+    <t>Quantity On Hand but Expired</t>
+  </si>
+  <si>
+    <t>&lt;quantityExpired&gt;</t>
   </si>
 </sst>
 </file>
@@ -743,9 +749,12 @@
         <v>9</v>
       </c>
       <c r="F8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -766,9 +775,12 @@
         <v>12</v>
       </c>
       <c r="F9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>17</v>
       </c>
       <c r="O9" s="1"/>

--- a/api/templates/devices_and_sites_overview/en.xlsx
+++ b/api/templates/devices_and_sites_overview/en.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\devices_and_sites_overview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71711033-3729-4CB7-A5A6-C469B5B85F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452AACFE-D75A-44DA-8C2B-5D5A4292CD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/api/templates/devices_and_sites_overview/en.xlsx
+++ b/api/templates/devices_and_sites_overview/en.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25726"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\devices_and_sites_overview\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\devices_and_sites_overview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452AACFE-D75A-44DA-8C2B-5D5A4292CD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="2052" windowWidth="29040" windowHeight="15840" tabRatio="815"/>
   </bookViews>
   <sheets>
-    <sheet name="Inventory by Site" sheetId="1" r:id="rId1"/>
+    <sheet name="Errors by Devices" sheetId="5" r:id="rId1"/>
+    <sheet name="Devices TB Reach" sheetId="2" r:id="rId2"/>
+    <sheet name="Error Codes" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -24,8 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
@@ -36,7 +35,127 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="110">
+  <si>
+    <t>Other Error</t>
+  </si>
+  <si>
+    <t>Total errors, invalid results, no results</t>
+  </si>
+  <si>
+    <t>Dates: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Run-time error</t>
+  </si>
+  <si>
+    <t>The actual temperature has drifted too far away from the setpoint</t>
+  </si>
+  <si>
+    <t>The temperature difference exceeds the limit</t>
+  </si>
+  <si>
+    <t>The internal instrument temperature was out of range</t>
+  </si>
+  <si>
+    <t>Optic signal of from detector exceeded the limit</t>
+  </si>
+  <si>
+    <t>Detector dark signal exceeded the limit</t>
+  </si>
+  <si>
+    <t>The power supply was detected to be out of range</t>
+  </si>
+  <si>
+    <t>The measured temperature of the optical system was not within the acceptable range</t>
+  </si>
+  <si>
+    <t>A valve positioning error was detected at the end of the run</t>
+  </si>
+  <si>
+    <t>Operation terminated error</t>
+  </si>
+  <si>
+    <t>Module is already running a test while performing command</t>
+  </si>
+  <si>
+    <t>Motion of the syringe drive was not detected</t>
+  </si>
+  <si>
+    <t>Syringe pressure reading exceeds the protocol limit</t>
+  </si>
+  <si>
+    <t>Syringe pressure reading is below the protocol limit</t>
+  </si>
+  <si>
+    <t>Cartridge loading error</t>
+  </si>
+  <si>
+    <t>Unable to initialize pressure sensor</t>
+  </si>
+  <si>
+    <t>The digital temperature reading for Thermistor A/Thermistor B/Ambient Thermistor/Optic Thermistor was not within the acceptable range</t>
+  </si>
+  <si>
+    <t>The system was unable to find the valve home position</t>
+  </si>
+  <si>
+    <t>Attempt to load a cartridge while the door is still closed</t>
+  </si>
+  <si>
+    <t>Failed to get to desired temperature</t>
+  </si>
+  <si>
+    <t>The system failed to find the plunger home position</t>
+  </si>
+  <si>
+    <t>The ultrasonic horn could not be tuned properly</t>
+  </si>
+  <si>
+    <t>The optical signal from Detector did not reach the expected value</t>
+  </si>
+  <si>
+    <t>The cartridge integrity test failed</t>
+  </si>
+  <si>
+    <t>Self-test error</t>
+  </si>
+  <si>
+    <t>Cooling fan operation was not verified. Measured temperature exceeded the limit</t>
+  </si>
+  <si>
+    <t>Post-run analysis error</t>
+  </si>
+  <si>
+    <t>Probe check failed. Probe check value was above the maximum</t>
+  </si>
+  <si>
+    <t>Probe check failed. Probe check value was below the minimum</t>
+  </si>
+  <si>
+    <t>Signal loss detected in the amplification curve</t>
+  </si>
+  <si>
+    <t>Serial</t>
+  </si>
+  <si>
+    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
+  </si>
   <si>
     <t>&lt;Table&gt;</t>
   </si>
@@ -44,74 +163,218 @@
     <t>&lt;siteName&gt;</t>
   </si>
   <si>
-    <t>Site</t>
-  </si>
-  <si>
-    <t>Dates: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
-  </si>
-  <si>
-    <t>Daily Consumption Rate</t>
-  </si>
-  <si>
-    <t>Days Stock Left</t>
-  </si>
-  <si>
-    <t>Quantity On Hand</t>
-  </si>
-  <si>
-    <t>Projected Annual Consumption</t>
-  </si>
-  <si>
-    <t>&lt;daysStockLeft&gt;</t>
-  </si>
-  <si>
-    <t>&lt;quantityOnHand&gt;</t>
-  </si>
-  <si>
-    <t>&lt;dailyConsumptionRate&gt;</t>
-  </si>
-  <si>
-    <t>Consumable</t>
-  </si>
-  <si>
-    <t>&lt;consumableName&gt;</t>
-  </si>
-  <si>
-    <t>Projected Waste</t>
-  </si>
-  <si>
-    <t>&lt;projectedWaste&gt;</t>
-  </si>
-  <si>
-    <t>&lt;projectedAnnualConsumption&gt;</t>
-  </si>
-  <si>
-    <t>Inventory by Site</t>
-  </si>
-  <si>
-    <t>Notes: this report only includes the consumables that were sometime tracked on the sites</t>
-  </si>
-  <si>
-    <t>Quantity On Hand but Expired</t>
-  </si>
-  <si>
-    <t>&lt;quantityExpired&gt;</t>
+    <t>Device</t>
+  </si>
+  <si>
+    <t>Type of error</t>
+  </si>
+  <si>
+    <t>&lt;deviceName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;5011&gt;</t>
+  </si>
+  <si>
+    <t>&lt;5007&gt;</t>
+  </si>
+  <si>
+    <t>&lt;5006&gt;</t>
+  </si>
+  <si>
+    <t>&lt;2008&gt;</t>
+  </si>
+  <si>
+    <t>&lt;2005&gt;</t>
+  </si>
+  <si>
+    <t>&lt;2037&gt;</t>
+  </si>
+  <si>
+    <t>&lt;2025&gt;</t>
+  </si>
+  <si>
+    <t>&lt;2022&gt;</t>
+  </si>
+  <si>
+    <t>&lt;otherErrors&gt;</t>
+  </si>
+  <si>
+    <t>&lt;invalidResults&gt;</t>
+  </si>
+  <si>
+    <t>Errors by Devices</t>
+  </si>
+  <si>
+    <t>Invalid results, no results</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Please note that this report includes MTB/Rif, MTB ULTRA and MTB XDR results</t>
+  </si>
+  <si>
+    <t>References</t>
+  </si>
+  <si>
+    <t># Days of interrupted service</t>
+  </si>
+  <si>
+    <t>Counts the number of days when a device was at least once reported with any of the inactivity statuses (including also the statuses Unknown and No Tests Performed)</t>
+  </si>
+  <si>
+    <t>Site name</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>District</t>
+  </si>
+  <si>
+    <t># MTB-</t>
+  </si>
+  <si>
+    <t># MTB+</t>
+  </si>
+  <si>
+    <t># MTB Trace Detected</t>
+  </si>
+  <si>
+    <t># MTB Error</t>
+  </si>
+  <si>
+    <t># MTB Invalid</t>
+  </si>
+  <si>
+    <t># MTB No Result</t>
+  </si>
+  <si>
+    <t># Rif Not Detected</t>
+  </si>
+  <si>
+    <t># Rif Detected</t>
+  </si>
+  <si>
+    <t># Rif Indeterminate</t>
+  </si>
+  <si>
+    <t># INH</t>
+  </si>
+  <si>
+    <t># FLQ</t>
+  </si>
+  <si>
+    <t># AMK</t>
+  </si>
+  <si>
+    <t># KAN</t>
+  </si>
+  <si>
+    <t># CAP</t>
+  </si>
+  <si>
+    <t># ETH</t>
+  </si>
+  <si>
+    <t># Modules used in the date range</t>
+  </si>
+  <si>
+    <t>Reason for interruption</t>
+  </si>
+  <si>
+    <t>Error rate</t>
+  </si>
+  <si>
+    <t>Error/Invalid rate</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t># Total tests</t>
+  </si>
+  <si>
+    <t>&lt;name&gt;</t>
+  </si>
+  <si>
+    <t>&lt;stateName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;districtName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;serial&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalMtbNegative&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalMtbDetected&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalMtbTraceDetected&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalErrors&gt;</t>
+  </si>
+  <si>
+    <t>&lt;mtbInvalid&gt;</t>
+  </si>
+  <si>
+    <t>&lt;mtbNoResult&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalMtbSens&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalMtbRes&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalMtbIndeterminate&gt;</t>
+  </si>
+  <si>
+    <t>&lt;INH&gt;</t>
+  </si>
+  <si>
+    <t>&lt;FLQ&gt;</t>
+  </si>
+  <si>
+    <t>&lt;AMK&gt;</t>
+  </si>
+  <si>
+    <t>&lt;KAN&gt;</t>
+  </si>
+  <si>
+    <t>&lt;CAP&gt;</t>
+  </si>
+  <si>
+    <t>&lt;ETH&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalXpertModulesInUse&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalInterruptedDays&gt;</t>
+  </si>
+  <si>
+    <t>&lt;reasonForInterruption&gt;</t>
+  </si>
+  <si>
+    <t>&lt;totalXpertTests&gt;</t>
+  </si>
+  <si>
+    <t>GeneXpert Devices for TB Reach</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -151,8 +414,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,12 +463,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF3CC0DD"/>
+        <bgColor rgb="FF00CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CC0DD"/>
+        <bgColor rgb="FF3CC0DD"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -189,6 +497,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -235,37 +558,70 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -338,11 +694,16 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="FF3CC0DD"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -675,126 +1036,731 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="23.3984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.69921875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.3984375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.09765625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.19921875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.69921875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="33.09765625" customWidth="1"/>
+    <col min="2" max="9" width="8.796875" style="3"/>
+    <col min="10" max="10" width="12.296875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.296875" style="3" customWidth="1"/>
+    <col min="12" max="12" width="15.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2"/>
-      <c r="C2" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-    </row>
-    <row r="3" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-    </row>
-    <row r="4" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="L8" s="28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26"/>
+      <c r="B9" s="29">
+        <v>5011</v>
+      </c>
+      <c r="C9" s="29">
+        <v>5007</v>
+      </c>
+      <c r="D9" s="29">
+        <v>5006</v>
+      </c>
+      <c r="E9" s="29">
+        <v>2008</v>
+      </c>
+      <c r="F9" s="29">
+        <v>2005</v>
+      </c>
+      <c r="G9" s="29">
+        <v>2037</v>
+      </c>
+      <c r="H9" s="29">
+        <v>2025</v>
+      </c>
+      <c r="I9" s="29">
+        <v>2022</v>
+      </c>
+      <c r="J9" s="29" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" s="3" t="e">
+        <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AMJ14"/>
+  <sheetFormatPr defaultColWidth="11.296875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.19921875" customWidth="1"/>
+    <col min="2" max="2" width="30.59765625" customWidth="1"/>
+    <col min="3" max="3" width="35.3984375" customWidth="1"/>
+    <col min="4" max="4" width="33.5" customWidth="1"/>
+    <col min="5" max="5" width="15.296875" customWidth="1"/>
+    <col min="6" max="8" width="11.59765625" customWidth="1"/>
+    <col min="9" max="10" width="15.59765625" customWidth="1"/>
+    <col min="11" max="11" width="13.59765625" customWidth="1"/>
+    <col min="12" max="13" width="11.59765625" customWidth="1"/>
+    <col min="14" max="21" width="15.59765625" customWidth="1"/>
+    <col min="22" max="23" width="20.59765625" customWidth="1"/>
+    <col min="24" max="25" width="20.59765625" style="8" customWidth="1"/>
+    <col min="26" max="26" width="33.296875" customWidth="1"/>
+    <col min="27" max="27" width="20.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1024" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+    </row>
+    <row r="2" spans="1:1024" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="O9" s="1"/>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1024" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="10"/>
+    </row>
+    <row r="4" spans="1:1024" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1024" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1024" ht="78" x14ac:dyDescent="0.3">
+      <c r="C6" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1024" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="13"/>
+    </row>
+    <row r="8" spans="1:1024" x14ac:dyDescent="0.3">
+      <c r="A8" s="14"/>
+    </row>
+    <row r="9" spans="1:1024" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1024" s="19" customFormat="1" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="P10" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="S10" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="T10" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="U10" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="V10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="W10" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="X10" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y10" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z10" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA10" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="AMH10"/>
+      <c r="AMI10"/>
+      <c r="AMJ10"/>
+    </row>
+    <row r="11" spans="1:1024" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="M11" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="N11" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="O11" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="P11" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="R11" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="S11" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="T11" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="U11" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="V11" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="W11" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="X11" s="22" t="e">
+        <f>IF(AA11=0,0,I11/AA11)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y11" s="23" t="e">
+        <f>IF(AA11=0,0,(I11+J11)/AA11)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z11" s="23" t="e">
+        <f>IF(Y11&gt;0.05,"High Rate of Errors/Invalids. Contact Lab.","")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AA11" s="20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1024" x14ac:dyDescent="0.3">
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C3:D3"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultRowHeight="21.9" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.19921875" customWidth="1"/>
+    <col min="3" max="3" width="100.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>1004</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>1005</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>1006</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>1007</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>1017</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>1018</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>2003</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>2005</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>2008</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>2009</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>2011</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>2014</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>2016</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
+        <v>2032</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>2034</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
+        <v>2037</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <v>4010</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
+        <v>4017</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>5006</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="4">
+        <v>5007</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
+        <v>5011</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/api/templates/devices_and_sites_overview/en.xlsx
+++ b/api/templates/devices_and_sites_overview/en.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\devices_and_sites_overview\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\devices_and_sites_overview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B924603-00AB-4817-B00D-903E54126B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171CED5B-8997-43C6-A97A-B715A6C1B7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GeneXpert Devices" sheetId="1" r:id="rId1"/>
@@ -411,10 +411,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d&quot;, &quot;yyyy;@"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm"/>
-    <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -523,25 +522,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -567,7 +554,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -580,16 +566,32 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -974,206 +976,206 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T12"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="15.19921875" customWidth="1"/>
-    <col min="5" max="5" width="31.09765625" customWidth="1"/>
+    <col min="4" max="4" width="15.25" customWidth="1"/>
+    <col min="5" max="5" width="31.125" customWidth="1"/>
     <col min="6" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="14.69921875" style="7" customWidth="1"/>
-    <col min="11" max="11" width="14.3984375" style="8" customWidth="1"/>
-    <col min="12" max="14" width="14.3984375" style="7" customWidth="1"/>
-    <col min="15" max="15" width="13.19921875" style="7" customWidth="1"/>
-    <col min="16" max="16" width="10.5" style="7" customWidth="1"/>
-    <col min="17" max="17" width="18.296875" style="7" customWidth="1"/>
-    <col min="18" max="18" width="11" style="8" customWidth="1"/>
+    <col min="10" max="10" width="14.75" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.375" style="4" customWidth="1"/>
+    <col min="12" max="14" width="14.375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="13.25" style="3" customWidth="1"/>
+    <col min="16" max="16" width="10.5" style="3" customWidth="1"/>
+    <col min="17" max="17" width="18.25" style="3" customWidth="1"/>
+    <col min="18" max="18" width="11" style="4" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="1015" max="1024" width="9.296875" customWidth="1"/>
+    <col min="1015" max="1024" width="9.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-    </row>
-    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="20" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="1:20" ht="57.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="20"/>
+    </row>
+    <row r="7" spans="1:20" ht="57.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="10"/>
-    </row>
-    <row r="9" spans="1:20" s="14" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" spans="1:20" s="10" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="L9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="13" t="s">
+      <c r="M9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="N9" s="13" t="s">
+      <c r="N9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="O9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="P9" s="13" t="s">
+      <c r="P9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="Q9" s="13" t="s">
+      <c r="Q9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="R9" s="13" t="s">
+      <c r="R9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="S9" s="12" t="s">
+      <c r="S9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="T9" s="12" t="s">
+      <c r="T9" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="I10" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="19" t="s">
+      <c r="J10" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="K10" s="20" t="s">
+      <c r="K10" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="M10" s="19" t="s">
+      <c r="M10" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="19" t="s">
+      <c r="N10" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="O10" s="19" t="s">
+      <c r="O10" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="P10" s="19" t="s">
+      <c r="P10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="Q10" s="19" t="s">
+      <c r="Q10" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="R10" s="20" t="s">
+      <c r="R10" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="S10" s="15" t="s">
+      <c r="S10" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="T10" s="15" t="s">
+      <c r="T10" s="11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1192,116 +1194,116 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.796875" customWidth="1"/>
-    <col min="2" max="2" width="17.3984375" customWidth="1"/>
-    <col min="3" max="3" width="21.09765625" customWidth="1"/>
-    <col min="4" max="4" width="27.19921875" customWidth="1"/>
-    <col min="5" max="5" width="16.09765625" customWidth="1"/>
-    <col min="6" max="6" width="25.69921875" customWidth="1"/>
-    <col min="7" max="7" width="13.796875" customWidth="1"/>
-    <col min="8" max="8" width="15.69921875" customWidth="1"/>
+    <col min="1" max="1" width="21.75" customWidth="1"/>
+    <col min="2" max="2" width="17.375" customWidth="1"/>
+    <col min="3" max="3" width="21.125" customWidth="1"/>
+    <col min="4" max="4" width="27.25" customWidth="1"/>
+    <col min="5" max="5" width="16.125" customWidth="1"/>
+    <col min="6" max="6" width="25.75" customWidth="1"/>
+    <col min="7" max="7" width="13.75" customWidth="1"/>
+    <col min="8" max="8" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="10"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C6" s="7"/>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="C7" s="7"/>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="11" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1317,142 +1319,142 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.09765625" customWidth="1"/>
-    <col min="2" max="9" width="8.796875" style="7" customWidth="1"/>
-    <col min="10" max="10" width="12.296875" style="7" customWidth="1"/>
-    <col min="11" max="11" width="14.296875" style="7" customWidth="1"/>
-    <col min="12" max="12" width="15.5" style="7" customWidth="1"/>
+    <col min="1" max="1" width="33.125" customWidth="1"/>
+    <col min="2" max="9" width="8.75" style="3" customWidth="1"/>
+    <col min="10" max="10" width="12.25" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.25" style="3" customWidth="1"/>
+    <col min="12" max="12" width="15.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="1" t="s">
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="25" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="25">
+    <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="23"/>
+      <c r="B9" s="1">
         <v>5011</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="1">
         <v>5007</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="1">
         <v>5006</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="1">
         <v>2008</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="1">
         <v>2005</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="1">
         <v>2037</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="1">
         <v>2025</v>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="1">
         <v>2022</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="23" t="s">
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="L10" s="7" t="e">
+      <c r="L10" s="3" t="e">
         <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10</f>
         <v>#VALUE!</v>
       </c>
@@ -1472,307 +1474,307 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.09765625" customWidth="1"/>
-    <col min="2" max="2" width="39.19921875" customWidth="1"/>
-    <col min="3" max="3" width="100.59765625" customWidth="1"/>
+    <col min="1" max="1" width="5.125" customWidth="1"/>
+    <col min="2" max="2" width="39.25" customWidth="1"/>
+    <col min="3" max="3" width="100.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="16" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26">
+    <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19">
         <v>1001</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="19" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="26">
+    <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19">
         <v>1002</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="19" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26">
+    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19">
         <v>1004</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="19" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26">
+    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
         <v>1005</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="19" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26">
+    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
         <v>1006</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="19" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26">
+    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
         <v>1007</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="19" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26">
+    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
         <v>1017</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="19" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26">
+    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
         <v>1018</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26">
+    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
         <v>2003</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="19" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26">
+    <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
         <v>2005</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="19" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26">
+    <row r="12" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
         <v>2008</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="19" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26">
+    <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
         <v>2009</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="19" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="26">
+    <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
         <v>2011</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="19" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26">
+    <row r="15" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
         <v>2014</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26">
+    <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
         <v>2016</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="19" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26">
+    <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
         <v>2018</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="19" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26">
+    <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
         <v>2022</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="19" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="26">
+    <row r="19" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
         <v>2025</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="19" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="26">
+    <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
         <v>2032</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="19" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26">
+    <row r="21" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
         <v>2034</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="19" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="26">
+    <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="19">
         <v>2037</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="19" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="26">
+    <row r="23" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="19">
         <v>4010</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="19" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="26">
+    <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="19">
         <v>4017</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="26">
+    <row r="25" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="19">
         <v>5006</v>
       </c>
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="19" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="26">
+    <row r="26" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="19">
         <v>5007</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="19" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="26">
+    <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
         <v>5011</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="19" t="s">
         <v>113</v>
       </c>
     </row>

--- a/api/templates/devices_and_sites_overview/en.xlsx
+++ b/api/templates/devices_and_sites_overview/en.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\devices_and_sites_overview\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gianatiempo/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171CED5B-8997-43C6-A97A-B715A6C1B7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F26E927-EE83-0748-AA0E-D95509292B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16440" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GeneXpert Devices" sheetId="1" r:id="rId1"/>
-    <sheet name="GeneXpert Inventory by Site" sheetId="2" r:id="rId2"/>
-    <sheet name="GeneXpert Errors by Devices" sheetId="3" r:id="rId3"/>
+    <sheet name="Xpert Site Summary Report" sheetId="1" r:id="rId1"/>
+    <sheet name="Xpert Site Inventory" sheetId="2" r:id="rId2"/>
+    <sheet name="Xpert Site Errors by Devices" sheetId="3" r:id="rId3"/>
     <sheet name="Error Codes" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -23,12 +23,8 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -40,9 +36,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="115">
-  <si>
-    <t>GeneXpert Devices</t>
-  </si>
   <si>
     <t>Dates: &lt;Dates&gt;</t>
   </si>
@@ -203,9 +196,6 @@
     <t>&lt;totalOtherTests&gt;</t>
   </si>
   <si>
-    <t>GeneXpert Inventory by Site</t>
-  </si>
-  <si>
     <t>Notes: this report only includes the consumables that were sometime tracked on the sites</t>
   </si>
   <si>
@@ -257,9 +247,6 @@
     <t>&lt;projectedWaste&gt;</t>
   </si>
   <si>
-    <t>GeneXpert Errors by Devices</t>
-  </si>
-  <si>
     <t>Type of error</t>
   </si>
   <si>
@@ -405,6 +392,15 @@
   </si>
   <si>
     <t>Last Result Update</t>
+  </si>
+  <si>
+    <t>Xpert Site Summary Report</t>
+  </si>
+  <si>
+    <t>Xpert Site Inventory</t>
+  </si>
+  <si>
+    <t>Xpert Site Errors by Devices</t>
   </si>
 </sst>
 </file>
@@ -571,27 +567,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -976,201 +972,201 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T12"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="15.25" customWidth="1"/>
-    <col min="5" max="5" width="31.125" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" customWidth="1"/>
+    <col min="5" max="5" width="31.1640625" customWidth="1"/>
     <col min="6" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="14.75" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.375" style="4" customWidth="1"/>
-    <col min="12" max="14" width="14.375" style="3" customWidth="1"/>
-    <col min="15" max="15" width="13.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" style="4" customWidth="1"/>
+    <col min="12" max="14" width="14.33203125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="13.1640625" style="3" customWidth="1"/>
     <col min="16" max="16" width="10.5" style="3" customWidth="1"/>
-    <col min="17" max="17" width="18.25" style="3" customWidth="1"/>
+    <col min="17" max="17" width="18.1640625" style="3" customWidth="1"/>
     <col min="18" max="18" width="11" style="4" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="1015" max="1024" width="9.25" customWidth="1"/>
+    <col min="1015" max="1024" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="20" t="s">
+    </row>
+    <row r="3" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="22"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="20"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E4" s="22"/>
+    </row>
+    <row r="5" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="20"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="E5" s="22"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="20"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="E6" s="22"/>
+    </row>
+    <row r="7" spans="1:20" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E7" s="22"/>
+    </row>
+    <row r="8" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>6</v>
-      </c>
-      <c r="E6" s="20"/>
-    </row>
-    <row r="7" spans="1:20" ht="57.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E7" s="20"/>
-    </row>
-    <row r="8" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" spans="1:20" s="10" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" s="10" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="H9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="I9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="J9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="K9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="L9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="M9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="N9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="O9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O9" s="9" t="s">
+      <c r="P9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="P9" s="9" t="s">
+      <c r="Q9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="Q9" s="9" t="s">
+      <c r="R9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="R9" s="9" t="s">
+      <c r="S9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="S9" s="8" t="s">
+      <c r="T9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="T9" s="8" t="s">
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="B10" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="E10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="F10" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="G10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="H10" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="I10" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="26" t="s">
+      <c r="J10" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="27" t="s">
+      <c r="K10" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="L10" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="L10" s="14" t="s">
+      <c r="M10" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="N10" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="14" t="s">
+      <c r="O10" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="O10" s="14" t="s">
+      <c r="P10" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="P10" s="14" t="s">
+      <c r="Q10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="Q10" s="14" t="s">
+      <c r="R10" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="R10" s="15" t="s">
+      <c r="S10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="S10" s="11" t="s">
+      <c r="T10" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="T10" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="16"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -1194,117 +1190,117 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.75" customWidth="1"/>
-    <col min="2" max="2" width="17.375" customWidth="1"/>
-    <col min="3" max="3" width="21.125" customWidth="1"/>
-    <col min="4" max="4" width="27.25" customWidth="1"/>
-    <col min="5" max="5" width="16.125" customWidth="1"/>
-    <col min="6" max="6" width="25.75" customWidth="1"/>
-    <col min="7" max="7" width="13.75" customWidth="1"/>
-    <col min="8" max="8" width="15.75" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.1640625" customWidth="1"/>
+    <col min="4" max="4" width="27.1640625" customWidth="1"/>
+    <col min="5" max="5" width="16.1640625" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="6"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="8" t="s">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="B9" s="11" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="D9" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="G9" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="H9" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1319,77 +1315,77 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.125" customWidth="1"/>
-    <col min="2" max="9" width="8.75" style="3" customWidth="1"/>
-    <col min="10" max="10" width="12.25" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.25" style="3" customWidth="1"/>
+    <col min="1" max="1" width="33.1640625" customWidth="1"/>
+    <col min="2" max="9" width="8.6640625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.1640625" style="3" customWidth="1"/>
     <col min="12" max="12" width="15.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="18" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>7</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="L8" s="25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="23"/>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="25"/>
       <c r="B9" s="1">
         <v>5011</v>
       </c>
@@ -1415,44 +1411,44 @@
         <v>2022</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="L10" s="3" t="e">
         <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10</f>
@@ -1474,308 +1470,308 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.125" customWidth="1"/>
-    <col min="2" max="2" width="39.25" customWidth="1"/>
-    <col min="3" max="3" width="100.625" customWidth="1"/>
+    <col min="1" max="1" width="5.1640625" customWidth="1"/>
+    <col min="2" max="2" width="39.1640625" customWidth="1"/>
+    <col min="3" max="3" width="100.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19">
         <v>1001</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="19">
         <v>1002</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="19">
         <v>1004</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="19">
         <v>1005</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="19">
         <v>1006</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19">
         <v>1007</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19">
         <v>1017</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19">
         <v>1018</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="19">
         <v>2003</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="19">
         <v>2005</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="19">
         <v>2008</v>
       </c>
       <c r="B12" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="19">
         <v>2009</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="19">
         <v>2011</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="19">
         <v>2014</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="19">
         <v>2016</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="19">
         <v>2018</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="19">
         <v>2022</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="19">
         <v>2025</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="19">
         <v>2032</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="19">
         <v>2034</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="19">
         <v>2037</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="19">
         <v>4010</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="19">
         <v>4017</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="19">
         <v>5006</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="19">
         <v>5007</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="19">
         <v>5011</v>
       </c>
       <c r="B27" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>110</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>
